--- a/data/12616002.xlsx
+++ b/data/12616002.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saura\Desktop\CAP776\CAP776-main\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8760044-3909-4A45-8F22-09440058889A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{061519C8-A355-4AB4-9AA2-00E50A273612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="38">
   <si>
     <t>My Data, My Story</t>
   </si>
@@ -165,6 +165,12 @@
   </si>
   <si>
     <t>MCA-D1P2633</t>
+  </si>
+  <si>
+    <t>2026-08-21</t>
+  </si>
+  <si>
+    <t>Consistent routine</t>
   </si>
 </sst>
 </file>
@@ -718,20 +724,50 @@
       </c>
     </row>
     <row r="6" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="3"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="6"/>
+      <c r="A6" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="4">
+        <v>498</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4">
+        <v>189</v>
+      </c>
+      <c r="E6" s="4">
+        <v>112</v>
+      </c>
+      <c r="F6" s="4">
+        <v>200</v>
+      </c>
+      <c r="G6" s="4">
+        <v>4</v>
+      </c>
+      <c r="H6" s="4">
+        <v>146</v>
+      </c>
+      <c r="I6" s="5">
+        <f>IF(COUNT(B6:F6,H6)&lt;6,"",SUM(B6:F6,H6))</f>
+        <v>1145</v>
+      </c>
+      <c r="J6" s="5">
+        <f>IF(I6="","",1440-I6)</f>
+        <v>295</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="7" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>

--- a/data/12616002.xlsx
+++ b/data/12616002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{061519C8-A355-4AB4-9AA2-00E50A273612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E30FCDB4-B002-4C88-BCA0-B96D1807ACC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Activity Log" sheetId="1" r:id="rId1"/>
     <sheet name="Lists" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="39">
   <si>
     <t>My Data, My Story</t>
   </si>
@@ -171,6 +171,9 @@
   </si>
   <si>
     <t>Consistent routine</t>
+  </si>
+  <si>
+    <t>2026-08-22</t>
   </si>
 </sst>
 </file>
@@ -770,20 +773,50 @@
       </c>
     </row>
     <row r="7" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="3"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="6"/>
+      <c r="A7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="4">
+        <v>467</v>
+      </c>
+      <c r="C7" s="13">
+        <v>40</v>
+      </c>
+      <c r="D7" s="13">
+        <v>141</v>
+      </c>
+      <c r="E7" s="13">
+        <v>261</v>
+      </c>
+      <c r="F7" s="13">
+        <v>0</v>
+      </c>
+      <c r="G7" s="13">
+        <v>0</v>
+      </c>
+      <c r="H7" s="13">
+        <v>170</v>
+      </c>
+      <c r="I7" s="5">
+        <f t="shared" ref="I7:I12" si="0">IF(COUNT(B7:F7,H7)&lt;6,"",SUM(B7:F7,H7))</f>
+        <v>1079</v>
+      </c>
+      <c r="J7" s="5">
+        <f>IF(I7="","",1440-I7)</f>
+        <v>361</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="8" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3"/>
@@ -794,7 +827,10 @@
       <c r="F8" s="13"/>
       <c r="G8" s="13"/>
       <c r="H8" s="13"/>
-      <c r="I8" s="5"/>
+      <c r="I8" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="J8" s="5"/>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -810,7 +846,10 @@
       <c r="F9" s="13"/>
       <c r="G9" s="13"/>
       <c r="H9" s="13"/>
-      <c r="I9" s="5"/>
+      <c r="I9" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="J9" s="5"/>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -826,7 +865,10 @@
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
       <c r="H10" s="13"/>
-      <c r="I10" s="5"/>
+      <c r="I10" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="J10" s="5"/>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -842,7 +884,10 @@
       <c r="F11" s="13"/>
       <c r="G11" s="13"/>
       <c r="H11" s="13"/>
-      <c r="I11" s="5"/>
+      <c r="I11" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="J11" s="5"/>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -858,7 +903,10 @@
       <c r="F12" s="13"/>
       <c r="G12" s="13"/>
       <c r="H12" s="13"/>
-      <c r="I12" s="5"/>
+      <c r="I12" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="J12" s="5"/>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>

--- a/data/12616002.xlsx
+++ b/data/12616002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E30FCDB4-B002-4C88-BCA0-B96D1807ACC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DB1E695-74D9-4402-B1ED-D2A019807C70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="41">
   <si>
     <t>My Data, My Story</t>
   </si>
@@ -174,6 +174,12 @@
   </si>
   <si>
     <t>2026-08-22</t>
+  </si>
+  <si>
+    <t>2026-08-23</t>
+  </si>
+  <si>
+    <t>High productivity</t>
   </si>
 </sst>
 </file>
@@ -819,23 +825,50 @@
       </c>
     </row>
     <row r="8" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="3"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="5" t="str">
+      <c r="A8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="4">
+        <v>539</v>
+      </c>
+      <c r="C8" s="13">
+        <v>40</v>
+      </c>
+      <c r="D8" s="13">
+        <v>94</v>
+      </c>
+      <c r="E8" s="13">
+        <v>107</v>
+      </c>
+      <c r="F8" s="13">
+        <v>0</v>
+      </c>
+      <c r="G8" s="13">
+        <v>0</v>
+      </c>
+      <c r="H8" s="13">
+        <v>260</v>
+      </c>
+      <c r="I8" s="5">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="5"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
-      <c r="N8" s="6"/>
+        <v>1040</v>
+      </c>
+      <c r="J8" s="5">
+        <f t="shared" ref="J8:J9" si="1">IF(I8="","",1440-I8)</f>
+        <v>400</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="9" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3"/>
@@ -850,7 +883,10 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J9" s="5"/>
+      <c r="J9" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>

--- a/data/12616002.xlsx
+++ b/data/12616002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DB1E695-74D9-4402-B1ED-D2A019807C70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1762F987-AB58-4379-BF85-305880BA1E59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="44">
   <si>
     <t>My Data, My Story</t>
   </si>
@@ -180,6 +180,15 @@
   </si>
   <si>
     <t>High productivity</t>
+  </si>
+  <si>
+    <t>2026-08-24</t>
+  </si>
+  <si>
+    <t>2026-08-25</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
   </si>
 </sst>
 </file>
@@ -854,7 +863,7 @@
         <v>1040</v>
       </c>
       <c r="J8" s="5">
-        <f t="shared" ref="J8:J9" si="1">IF(I8="","",1440-I8)</f>
+        <f t="shared" ref="J8:J11" si="1">IF(I8="","",1440-I8)</f>
         <v>400</v>
       </c>
       <c r="K8" s="4" t="s">
@@ -871,64 +880,142 @@
       </c>
     </row>
     <row r="9" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="3"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="5" t="str">
+      <c r="A9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="4">
+        <v>560</v>
+      </c>
+      <c r="C9" s="13">
+        <v>40</v>
+      </c>
+      <c r="D9" s="13">
+        <v>129</v>
+      </c>
+      <c r="E9" s="13">
+        <v>94</v>
+      </c>
+      <c r="F9" s="13">
+        <v>200</v>
+      </c>
+      <c r="G9" s="13">
+        <v>4</v>
+      </c>
+      <c r="H9" s="13">
+        <v>260</v>
+      </c>
+      <c r="I9" s="5">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="5" t="str">
+        <v>1283</v>
+      </c>
+      <c r="J9" s="5">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
-      <c r="N9" s="6"/>
+        <v>157</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="N9" s="6" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="10" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="3"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="5" t="str">
+      <c r="A10" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="4">
+        <v>487</v>
+      </c>
+      <c r="C10" s="13">
+        <v>30</v>
+      </c>
+      <c r="D10" s="13">
+        <v>127</v>
+      </c>
+      <c r="E10" s="13">
+        <v>78</v>
+      </c>
+      <c r="F10" s="13">
+        <v>200</v>
+      </c>
+      <c r="G10" s="13">
+        <v>4</v>
+      </c>
+      <c r="H10" s="13">
+        <v>158</v>
+      </c>
+      <c r="I10" s="5">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="5"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
-      <c r="N10" s="6"/>
+        <v>1080</v>
+      </c>
+      <c r="J10" s="5">
+        <f t="shared" si="1"/>
+        <v>360</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="N10" s="6" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="11" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="3"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="5" t="str">
+      <c r="A11" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" s="4">
+        <v>472</v>
+      </c>
+      <c r="C11" s="13">
+        <v>60</v>
+      </c>
+      <c r="D11" s="13">
+        <v>145</v>
+      </c>
+      <c r="E11" s="13">
+        <v>200</v>
+      </c>
+      <c r="F11" s="13">
+        <v>150</v>
+      </c>
+      <c r="G11" s="13">
+        <v>3</v>
+      </c>
+      <c r="H11" s="13">
+        <v>148</v>
+      </c>
+      <c r="I11" s="5">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="5"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
-      <c r="N11" s="6"/>
+        <v>1175</v>
+      </c>
+      <c r="J11" s="5">
+        <f t="shared" si="1"/>
+        <v>265</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="12" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3"/>

--- a/data/12616002.xlsx
+++ b/data/12616002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1762F987-AB58-4379-BF85-305880BA1E59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21ECE481-DEA0-4027-95F8-DD91BB641484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -863,7 +863,7 @@
         <v>1040</v>
       </c>
       <c r="J8" s="5">
-        <f t="shared" ref="J8:J11" si="1">IF(I8="","",1440-I8)</f>
+        <f t="shared" ref="J8:J12" si="1">IF(I8="","",1440-I8)</f>
         <v>400</v>
       </c>
       <c r="K8" s="4" t="s">
@@ -1026,10 +1026,7 @@
       <c r="F12" s="13"/>
       <c r="G12" s="13"/>
       <c r="H12" s="13"/>
-      <c r="I12" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="I12" s="5"/>
       <c r="J12" s="5"/>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>

--- a/data/12616002.xlsx
+++ b/data/12616002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21ECE481-DEA0-4027-95F8-DD91BB641484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{939E96D4-5208-4A77-8EFA-C0D4D4AB85CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="45">
   <si>
     <t>My Data, My Story</t>
   </si>
@@ -189,6 +189,9 @@
   </si>
   <si>
     <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>Balanced day</t>
   </si>
 </sst>
 </file>
@@ -1018,20 +1021,50 @@
       </c>
     </row>
     <row r="12" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="3"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
-      <c r="N12" s="6"/>
+      <c r="A12" s="3">
+        <v>46261</v>
+      </c>
+      <c r="B12" s="4">
+        <v>527</v>
+      </c>
+      <c r="C12" s="13">
+        <v>0</v>
+      </c>
+      <c r="D12" s="13">
+        <v>73</v>
+      </c>
+      <c r="E12" s="13">
+        <v>76</v>
+      </c>
+      <c r="F12" s="13">
+        <v>200</v>
+      </c>
+      <c r="G12" s="13">
+        <v>4</v>
+      </c>
+      <c r="H12" s="13">
+        <v>123</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" si="0"/>
+        <v>999</v>
+      </c>
+      <c r="J12" s="5">
+        <f t="shared" si="1"/>
+        <v>441</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="N12" s="6" t="s">
+        <v>44</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/12616002.xlsx
+++ b/data/12616002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{939E96D4-5208-4A77-8EFA-C0D4D4AB85CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98306046-73B2-4D52-85F9-59EABC197BFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="39">
   <si>
     <t>My Data, My Story</t>
   </si>
@@ -167,28 +167,10 @@
     <t>MCA-D1P2633</t>
   </si>
   <si>
-    <t>2026-08-21</t>
-  </si>
-  <si>
     <t>Consistent routine</t>
   </si>
   <si>
-    <t>2026-08-22</t>
-  </si>
-  <si>
-    <t>2026-08-23</t>
-  </si>
-  <si>
     <t>High productivity</t>
-  </si>
-  <si>
-    <t>2026-08-24</t>
-  </si>
-  <si>
-    <t>2026-08-25</t>
-  </si>
-  <si>
-    <t>2026-08-26</t>
   </si>
   <si>
     <t>Balanced day</t>
@@ -198,10 +180,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-  </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -249,6 +228,12 @@
       <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -336,9 +321,6 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -357,6 +339,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -640,7 +625,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N53"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.1796875" bestFit="1" customWidth="1"/>
@@ -676,24 +661,24 @@
       <c r="N1" s="14"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="11">
+      <c r="F2" s="10">
         <v>12616002</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="11" t="s">
         <v>35</v>
       </c>
     </row>
@@ -701,22 +686,22 @@
       <c r="A4" s="1"/>
     </row>
     <row r="5" spans="1:14" ht="61.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="8" t="s">
         <v>9</v>
       </c>
       <c r="G5" s="2" t="s">
@@ -745,333 +730,1340 @@
       </c>
     </row>
     <row r="6" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6" s="4">
+      <c r="A6" s="13">
+        <v>46255</v>
+      </c>
+      <c r="B6" s="3">
         <v>498</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="3">
         <v>0</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="3">
         <v>189</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="3">
         <v>112</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="3">
         <v>200</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="3">
         <v>4</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6" s="3">
         <v>146</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I6" s="4">
         <f>IF(COUNT(B6:F6,H6)&lt;6,"",SUM(B6:F6,H6))</f>
         <v>1145</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J6" s="4">
         <f>IF(I6="","",1440-I6)</f>
         <v>295</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="L6" s="4" t="s">
+      <c r="L6" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="M6" s="4" t="s">
+      <c r="M6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="N6" s="6" t="s">
-        <v>37</v>
+      <c r="N6" s="5" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7" s="4">
+      <c r="A7" s="13">
+        <v>46256</v>
+      </c>
+      <c r="B7" s="3">
         <v>467</v>
       </c>
-      <c r="C7" s="13">
+      <c r="C7" s="12">
         <v>40</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="12">
         <v>141</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="12">
         <v>261</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="12">
         <v>0</v>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="12">
         <v>0</v>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="12">
         <v>170</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7" s="4">
         <f t="shared" ref="I7:I12" si="0">IF(COUNT(B7:F7,H7)&lt;6,"",SUM(B7:F7,H7))</f>
         <v>1079</v>
       </c>
-      <c r="J7" s="5">
+      <c r="J7" s="4">
         <f>IF(I7="","",1440-I7)</f>
         <v>361</v>
       </c>
-      <c r="K7" s="4" t="s">
+      <c r="K7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="L7" s="4" t="s">
+      <c r="L7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="M7" s="4" t="s">
+      <c r="M7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="N7" s="6" t="s">
-        <v>37</v>
+      <c r="N7" s="5" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B8" s="4">
+      <c r="A8" s="13">
+        <v>46257</v>
+      </c>
+      <c r="B8" s="3">
         <v>539</v>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="12">
         <v>40</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="12">
         <v>94</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="12">
         <v>107</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="12">
         <v>0</v>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="12">
         <v>0</v>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="12">
         <v>260</v>
       </c>
-      <c r="I8" s="5">
+      <c r="I8" s="4">
         <f t="shared" si="0"/>
         <v>1040</v>
       </c>
-      <c r="J8" s="5">
+      <c r="J8" s="4">
         <f t="shared" ref="J8:J12" si="1">IF(I8="","",1440-I8)</f>
         <v>400</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="K8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L8" s="4" t="s">
+      <c r="L8" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="M8" s="4" t="s">
+      <c r="M8" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="N8" s="6" t="s">
+      <c r="N8" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="13">
+        <v>46258</v>
+      </c>
+      <c r="B9" s="3">
+        <v>560</v>
+      </c>
+      <c r="C9" s="12">
         <v>40</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B9" s="4">
-        <v>560</v>
-      </c>
-      <c r="C9" s="13">
-        <v>40</v>
-      </c>
-      <c r="D9" s="13">
+      <c r="D9" s="12">
         <v>129</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="12">
         <v>94</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="12">
         <v>200</v>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="12">
         <v>4</v>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="12">
         <v>260</v>
       </c>
-      <c r="I9" s="5">
+      <c r="I9" s="4">
         <f t="shared" si="0"/>
         <v>1283</v>
       </c>
-      <c r="J9" s="5">
+      <c r="J9" s="4">
         <f t="shared" si="1"/>
         <v>157</v>
       </c>
-      <c r="K9" s="4" t="s">
+      <c r="K9" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="L9" s="4" t="s">
+      <c r="L9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="M9" s="4" t="s">
+      <c r="M9" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="N9" s="6" t="s">
-        <v>37</v>
+      <c r="N9" s="5" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B10" s="4">
+      <c r="A10" s="13">
+        <v>46259</v>
+      </c>
+      <c r="B10" s="3">
         <v>487</v>
       </c>
-      <c r="C10" s="13">
+      <c r="C10" s="12">
         <v>30</v>
       </c>
-      <c r="D10" s="13">
+      <c r="D10" s="12">
         <v>127</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="12">
         <v>78</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="12">
         <v>200</v>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="12">
         <v>4</v>
       </c>
-      <c r="H10" s="13">
+      <c r="H10" s="12">
         <v>158</v>
       </c>
-      <c r="I10" s="5">
+      <c r="I10" s="4">
         <f t="shared" si="0"/>
         <v>1080</v>
       </c>
-      <c r="J10" s="5">
+      <c r="J10" s="4">
         <f t="shared" si="1"/>
         <v>360</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="K10" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L10" s="4" t="s">
+      <c r="L10" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="M10" s="4" t="s">
+      <c r="M10" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="N10" s="6" t="s">
-        <v>40</v>
+      <c r="N10" s="5" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B11" s="4">
+      <c r="A11" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B11" s="3">
         <v>472</v>
       </c>
-      <c r="C11" s="13">
+      <c r="C11" s="12">
         <v>60</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="12">
         <v>145</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="12">
         <v>200</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="12">
         <v>150</v>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="12">
         <v>3</v>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="12">
         <v>148</v>
       </c>
-      <c r="I11" s="5">
+      <c r="I11" s="4">
         <f t="shared" si="0"/>
         <v>1175</v>
       </c>
-      <c r="J11" s="5">
+      <c r="J11" s="4">
         <f t="shared" si="1"/>
         <v>265</v>
       </c>
-      <c r="K11" s="4" t="s">
+      <c r="K11" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L11" s="4" t="s">
+      <c r="L11" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="M11" s="4" t="s">
+      <c r="M11" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="N11" s="6" t="s">
-        <v>37</v>
+      <c r="N11" s="5" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="3">
+      <c r="A12" s="13">
         <v>46261</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="3">
         <v>527</v>
       </c>
-      <c r="C12" s="13">
+      <c r="C12" s="12">
         <v>0</v>
       </c>
-      <c r="D12" s="13">
+      <c r="D12" s="12">
         <v>73</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="12">
         <v>76</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="12">
         <v>200</v>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="12">
         <v>4</v>
       </c>
-      <c r="H12" s="13">
+      <c r="H12" s="12">
         <v>123</v>
       </c>
-      <c r="I12" s="5">
+      <c r="I12" s="4">
         <f t="shared" si="0"/>
         <v>999</v>
       </c>
-      <c r="J12" s="5">
+      <c r="J12" s="4">
         <f t="shared" si="1"/>
         <v>441</v>
       </c>
-      <c r="K12" s="4" t="s">
+      <c r="K12" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="L12" s="4" t="s">
+      <c r="L12" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="M12" s="4" t="s">
+      <c r="M12" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="N12" s="6" t="s">
-        <v>44</v>
-      </c>
+      <c r="N12" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A13" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B13" s="3">
+        <v>391</v>
+      </c>
+      <c r="C13" s="12">
+        <v>30</v>
+      </c>
+      <c r="D13" s="12">
+        <v>112</v>
+      </c>
+      <c r="E13" s="12">
+        <v>190</v>
+      </c>
+      <c r="F13" s="12">
+        <v>200</v>
+      </c>
+      <c r="G13" s="12">
+        <v>4</v>
+      </c>
+      <c r="H13" s="12">
+        <v>157</v>
+      </c>
+      <c r="I13" s="4">
+        <f t="shared" ref="I13:I53" si="2">IF(COUNT(B13:F13,H13)&lt;6,"",SUM(B13:F13,H13))</f>
+        <v>1080</v>
+      </c>
+      <c r="J13" s="4">
+        <f t="shared" ref="J13:J53" si="3">IF(I13="","",1440-I13)</f>
+        <v>360</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="N13" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A14" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B14" s="3"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J14" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="5"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A15" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B15" s="3"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J15" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="5"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A16" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B16" s="3"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J16" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="5"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A17" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B17" s="3"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J17" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="5"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A18" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B18" s="3"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J18" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="5"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A19" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B19" s="3"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J19" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="5"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A20" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B20" s="3"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J20" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="5"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A21" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B21" s="3"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J21" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
+      <c r="N21" s="5"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A22" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B22" s="3"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J22" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="5"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A23" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B23" s="3"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J23" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="5"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A24" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B24" s="3"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J24" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="5"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A25" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B25" s="3"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J25" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
+      <c r="N25" s="5"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A26" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B26" s="3"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J26" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3"/>
+      <c r="M26" s="3"/>
+      <c r="N26" s="5"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A27" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B27" s="3"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J27" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K27" s="3"/>
+      <c r="L27" s="3"/>
+      <c r="M27" s="3"/>
+      <c r="N27" s="5"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A28" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B28" s="3"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J28" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="5"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A29" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B29" s="3"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J29" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K29" s="3"/>
+      <c r="L29" s="3"/>
+      <c r="M29" s="3"/>
+      <c r="N29" s="5"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A30" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B30" s="3"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J30" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="3"/>
+      <c r="N30" s="5"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A31" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B31" s="3"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="12"/>
+      <c r="I31" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J31" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K31" s="3"/>
+      <c r="L31" s="3"/>
+      <c r="M31" s="3"/>
+      <c r="N31" s="5"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A32" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B32" s="3"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J32" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3"/>
+      <c r="M32" s="3"/>
+      <c r="N32" s="5"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A33" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B33" s="3"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="12"/>
+      <c r="I33" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J33" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K33" s="3"/>
+      <c r="L33" s="3"/>
+      <c r="M33" s="3"/>
+      <c r="N33" s="5"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A34" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B34" s="3"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="12"/>
+      <c r="I34" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J34" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K34" s="3"/>
+      <c r="L34" s="3"/>
+      <c r="M34" s="3"/>
+      <c r="N34" s="5"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A35" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B35" s="3"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="12"/>
+      <c r="I35" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J35" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K35" s="3"/>
+      <c r="L35" s="3"/>
+      <c r="M35" s="3"/>
+      <c r="N35" s="5"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A36" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B36" s="3"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="12"/>
+      <c r="H36" s="12"/>
+      <c r="I36" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J36" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K36" s="3"/>
+      <c r="L36" s="3"/>
+      <c r="M36" s="3"/>
+      <c r="N36" s="5"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A37" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B37" s="3"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12"/>
+      <c r="H37" s="12"/>
+      <c r="I37" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J37" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K37" s="3"/>
+      <c r="L37" s="3"/>
+      <c r="M37" s="3"/>
+      <c r="N37" s="5"/>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A38" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B38" s="3"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12"/>
+      <c r="H38" s="12"/>
+      <c r="I38" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J38" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K38" s="3"/>
+      <c r="L38" s="3"/>
+      <c r="M38" s="3"/>
+      <c r="N38" s="5"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A39" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B39" s="3"/>
+      <c r="C39" s="12"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="12"/>
+      <c r="H39" s="12"/>
+      <c r="I39" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J39" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K39" s="3"/>
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+      <c r="N39" s="5"/>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A40" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B40" s="3"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="12"/>
+      <c r="H40" s="12"/>
+      <c r="I40" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J40" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K40" s="3"/>
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+      <c r="N40" s="5"/>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A41" s="13">
+        <v>46290</v>
+      </c>
+      <c r="B41" s="3"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="12"/>
+      <c r="H41" s="12"/>
+      <c r="I41" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J41" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K41" s="3"/>
+      <c r="L41" s="3"/>
+      <c r="M41" s="3"/>
+      <c r="N41" s="5"/>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A42" s="13">
+        <v>46291</v>
+      </c>
+      <c r="B42" s="3"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="12"/>
+      <c r="H42" s="12"/>
+      <c r="I42" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J42" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K42" s="3"/>
+      <c r="L42" s="3"/>
+      <c r="M42" s="3"/>
+      <c r="N42" s="5"/>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A43" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B43" s="3"/>
+      <c r="C43" s="12"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12"/>
+      <c r="H43" s="12"/>
+      <c r="I43" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J43" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K43" s="3"/>
+      <c r="L43" s="3"/>
+      <c r="M43" s="3"/>
+      <c r="N43" s="5"/>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A44" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B44" s="3"/>
+      <c r="C44" s="12"/>
+      <c r="D44" s="12"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="12"/>
+      <c r="G44" s="12"/>
+      <c r="H44" s="12"/>
+      <c r="I44" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J44" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K44" s="3"/>
+      <c r="L44" s="3"/>
+      <c r="M44" s="3"/>
+      <c r="N44" s="5"/>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A45" s="13">
+        <v>46294</v>
+      </c>
+      <c r="B45" s="3"/>
+      <c r="C45" s="12"/>
+      <c r="D45" s="12"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="12"/>
+      <c r="G45" s="12"/>
+      <c r="H45" s="12"/>
+      <c r="I45" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J45" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K45" s="3"/>
+      <c r="L45" s="3"/>
+      <c r="M45" s="3"/>
+      <c r="N45" s="5"/>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A46" s="13">
+        <v>46295</v>
+      </c>
+      <c r="B46" s="3"/>
+      <c r="C46" s="12"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="12"/>
+      <c r="H46" s="12"/>
+      <c r="I46" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J46" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K46" s="3"/>
+      <c r="L46" s="3"/>
+      <c r="M46" s="3"/>
+      <c r="N46" s="5"/>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A47" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B47" s="3"/>
+      <c r="C47" s="12"/>
+      <c r="D47" s="12"/>
+      <c r="E47" s="12"/>
+      <c r="F47" s="12"/>
+      <c r="G47" s="12"/>
+      <c r="H47" s="12"/>
+      <c r="I47" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J47" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K47" s="3"/>
+      <c r="L47" s="3"/>
+      <c r="M47" s="3"/>
+      <c r="N47" s="5"/>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A48" s="13">
+        <v>46297</v>
+      </c>
+      <c r="B48" s="3"/>
+      <c r="C48" s="12"/>
+      <c r="D48" s="12"/>
+      <c r="E48" s="12"/>
+      <c r="F48" s="12"/>
+      <c r="G48" s="12"/>
+      <c r="H48" s="12"/>
+      <c r="I48" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J48" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K48" s="3"/>
+      <c r="L48" s="3"/>
+      <c r="M48" s="3"/>
+      <c r="N48" s="5"/>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A49" s="13">
+        <v>46298</v>
+      </c>
+      <c r="B49" s="3"/>
+      <c r="C49" s="12"/>
+      <c r="D49" s="12"/>
+      <c r="E49" s="12"/>
+      <c r="F49" s="12"/>
+      <c r="G49" s="12"/>
+      <c r="H49" s="12"/>
+      <c r="I49" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J49" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K49" s="3"/>
+      <c r="L49" s="3"/>
+      <c r="M49" s="3"/>
+      <c r="N49" s="5"/>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A50" s="13">
+        <v>46299</v>
+      </c>
+      <c r="B50" s="3"/>
+      <c r="C50" s="12"/>
+      <c r="D50" s="12"/>
+      <c r="E50" s="12"/>
+      <c r="F50" s="12"/>
+      <c r="G50" s="12"/>
+      <c r="H50" s="12"/>
+      <c r="I50" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J50" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K50" s="3"/>
+      <c r="L50" s="3"/>
+      <c r="M50" s="3"/>
+      <c r="N50" s="5"/>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A51" s="13">
+        <v>46300</v>
+      </c>
+      <c r="B51" s="3"/>
+      <c r="C51" s="12"/>
+      <c r="D51" s="12"/>
+      <c r="E51" s="12"/>
+      <c r="F51" s="12"/>
+      <c r="G51" s="12"/>
+      <c r="H51" s="12"/>
+      <c r="I51" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J51" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K51" s="3"/>
+      <c r="L51" s="3"/>
+      <c r="M51" s="3"/>
+      <c r="N51" s="5"/>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A52" s="13">
+        <v>46301</v>
+      </c>
+      <c r="B52" s="3"/>
+      <c r="C52" s="12"/>
+      <c r="D52" s="12"/>
+      <c r="E52" s="12"/>
+      <c r="F52" s="12"/>
+      <c r="G52" s="12"/>
+      <c r="H52" s="12"/>
+      <c r="I52" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J52" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K52" s="3"/>
+      <c r="L52" s="3"/>
+      <c r="M52" s="3"/>
+      <c r="N52" s="5"/>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A53" s="13">
+        <v>46302</v>
+      </c>
+      <c r="B53" s="3"/>
+      <c r="C53" s="12"/>
+      <c r="D53" s="12"/>
+      <c r="E53" s="12"/>
+      <c r="F53" s="12"/>
+      <c r="G53" s="12"/>
+      <c r="H53" s="12"/>
+      <c r="I53" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J53" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K53" s="3"/>
+      <c r="L53" s="3"/>
+      <c r="M53" s="3"/>
+      <c r="N53" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
-  <conditionalFormatting sqref="I6:J12">
-    <cfRule type="expression" dxfId="0" priority="2">
+  <phoneticPr fontId="8" type="noConversion"/>
+  <conditionalFormatting sqref="I6:J53">
+    <cfRule type="expression" dxfId="0" priority="4">
       <formula>AND(ISNUMBER($I6),$I6&gt;1440)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1098,7 +2090,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>K6:K12</xm:sqref>
+          <xm:sqref>K6:K53</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from list" error="Choose a value from the dropdown." xr:uid="{00000000-0002-0000-0000-000003000000}">
           <x14:formula1>
@@ -1107,7 +2099,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>L6:L12</xm:sqref>
+          <xm:sqref>L6:L53</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from list" error="Choose a value from the dropdown." xr:uid="{00000000-0002-0000-0000-000004000000}">
           <x14:formula1>
@@ -1116,7 +2108,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>M6:M12</xm:sqref>
+          <xm:sqref>M6:M53</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1138,110 +2130,110 @@
       <c r="A1" s="1"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="6" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="7">
         <v>5</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="7">
         <v>5</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H4" s="7">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="7">
         <v>4</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="7">
         <v>4</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="7">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="7">
         <v>3</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="7">
         <v>3</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="7">
         <v>2</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="7">
         <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="7">
         <v>1</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="7">
         <v>1</v>
       </c>
     </row>

--- a/data/12616002.xlsx
+++ b/data/12616002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98306046-73B2-4D52-85F9-59EABC197BFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{229CF9D7-E510-4D38-8FC0-D82DD8B39DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="40">
   <si>
     <t>My Data, My Story</t>
   </si>
@@ -174,6 +174,9 @@
   </si>
   <si>
     <t>Balanced day</t>
+  </si>
+  <si>
+    <t>2026-08-29</t>
   </si>
 </sst>
 </file>
@@ -1098,28 +1101,50 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A14" s="13">
-        <v>46263</v>
-      </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J14" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="5"/>
+      <c r="A14" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="3">
+        <v>413</v>
+      </c>
+      <c r="C14" s="12">
+        <v>0</v>
+      </c>
+      <c r="D14" s="12">
+        <v>102</v>
+      </c>
+      <c r="E14" s="12">
+        <v>174</v>
+      </c>
+      <c r="F14" s="12">
+        <v>0</v>
+      </c>
+      <c r="G14" s="12">
+        <v>0</v>
+      </c>
+      <c r="H14" s="12">
+        <v>280</v>
+      </c>
+      <c r="I14" s="4">
+        <f t="shared" si="2"/>
+        <v>969</v>
+      </c>
+      <c r="J14" s="4">
+        <f t="shared" si="3"/>
+        <v>471</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="N14" s="5" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="13">

--- a/data/12616002.xlsx
+++ b/data/12616002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{229CF9D7-E510-4D38-8FC0-D82DD8B39DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3085AAD-3BF1-434F-83EC-FFAC6E4D9CF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="40">
   <si>
     <t>My Data, My Story</t>
   </si>
@@ -1150,25 +1150,47 @@
       <c r="A15" s="13">
         <v>46264</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J15" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="5"/>
+      <c r="B15" s="3">
+        <v>454</v>
+      </c>
+      <c r="C15" s="12">
+        <v>0</v>
+      </c>
+      <c r="D15" s="12">
+        <v>127</v>
+      </c>
+      <c r="E15" s="12">
+        <v>149</v>
+      </c>
+      <c r="F15" s="12">
+        <v>0</v>
+      </c>
+      <c r="G15" s="12">
+        <v>0</v>
+      </c>
+      <c r="H15" s="12">
+        <v>209</v>
+      </c>
+      <c r="I15" s="4">
+        <f t="shared" si="2"/>
+        <v>939</v>
+      </c>
+      <c r="J15" s="4">
+        <f t="shared" si="3"/>
+        <v>501</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N15" s="5" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="13">

--- a/data/12616002.xlsx
+++ b/data/12616002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3085AAD-3BF1-434F-83EC-FFAC6E4D9CF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46C2A3A3-DD29-4F55-935F-93F63193F793}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="41">
   <si>
     <t>My Data, My Story</t>
   </si>
@@ -177,6 +177,9 @@
   </si>
   <si>
     <t>2026-08-29</t>
+  </si>
+  <si>
+    <t>Good Learning</t>
   </si>
 </sst>
 </file>
@@ -1196,25 +1199,47 @@
       <c r="A16" s="13">
         <v>46265</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J16" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="5"/>
+      <c r="B16" s="3">
+        <v>475</v>
+      </c>
+      <c r="C16" s="12">
+        <v>60</v>
+      </c>
+      <c r="D16" s="12">
+        <v>126</v>
+      </c>
+      <c r="E16" s="12">
+        <v>284</v>
+      </c>
+      <c r="F16" s="12">
+        <v>200</v>
+      </c>
+      <c r="G16" s="12">
+        <v>4</v>
+      </c>
+      <c r="H16" s="12">
+        <v>150</v>
+      </c>
+      <c r="I16" s="4">
+        <f t="shared" si="2"/>
+        <v>1295</v>
+      </c>
+      <c r="J16" s="4">
+        <f t="shared" si="3"/>
+        <v>145</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N16" s="5" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="13">

--- a/data/12616002.xlsx
+++ b/data/12616002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46C2A3A3-DD29-4F55-935F-93F63193F793}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C3C3ED2-BDF4-4586-89B2-054BCEDBD4B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="41">
   <si>
     <t>My Data, My Story</t>
   </si>
@@ -1245,25 +1245,47 @@
       <c r="A17" s="13">
         <v>46266</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J17" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="5"/>
+      <c r="B17" s="3">
+        <v>466</v>
+      </c>
+      <c r="C17" s="12">
+        <v>0</v>
+      </c>
+      <c r="D17" s="12">
+        <v>129</v>
+      </c>
+      <c r="E17" s="12">
+        <v>132</v>
+      </c>
+      <c r="F17" s="12">
+        <v>200</v>
+      </c>
+      <c r="G17" s="12">
+        <v>4</v>
+      </c>
+      <c r="H17" s="12">
+        <v>193</v>
+      </c>
+      <c r="I17" s="4">
+        <f t="shared" si="2"/>
+        <v>1120</v>
+      </c>
+      <c r="J17" s="4">
+        <f t="shared" si="3"/>
+        <v>320</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N17" s="5" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="13">

--- a/data/12616002.xlsx
+++ b/data/12616002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C3C3ED2-BDF4-4586-89B2-054BCEDBD4B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FE44C21-5ADD-4AE4-8866-495503CDBE0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="41">
   <si>
     <t>My Data, My Story</t>
   </si>
@@ -1291,25 +1291,47 @@
       <c r="A18" s="13">
         <v>46267</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J18" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
-      <c r="N18" s="5"/>
+      <c r="B18" s="3">
+        <v>467</v>
+      </c>
+      <c r="C18" s="12">
+        <v>30</v>
+      </c>
+      <c r="D18" s="12">
+        <v>140</v>
+      </c>
+      <c r="E18" s="12">
+        <v>184</v>
+      </c>
+      <c r="F18" s="12">
+        <v>200</v>
+      </c>
+      <c r="G18" s="12">
+        <v>4</v>
+      </c>
+      <c r="H18" s="12">
+        <v>133</v>
+      </c>
+      <c r="I18" s="4">
+        <f t="shared" si="2"/>
+        <v>1154</v>
+      </c>
+      <c r="J18" s="4">
+        <f t="shared" si="3"/>
+        <v>286</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N18" s="5" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="13">

--- a/data/12616002.xlsx
+++ b/data/12616002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FE44C21-5ADD-4AE4-8866-495503CDBE0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA391D56-681A-4E05-90DE-44C9F8083A89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="41">
   <si>
     <t>My Data, My Story</t>
   </si>
@@ -1337,25 +1337,47 @@
       <c r="A19" s="13">
         <v>46268</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J19" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
-      <c r="N19" s="5"/>
+      <c r="B19" s="3">
+        <v>492</v>
+      </c>
+      <c r="C19" s="12">
+        <v>30</v>
+      </c>
+      <c r="D19" s="12">
+        <v>114</v>
+      </c>
+      <c r="E19" s="12">
+        <v>98</v>
+      </c>
+      <c r="F19" s="12">
+        <v>150</v>
+      </c>
+      <c r="G19" s="12">
+        <v>3</v>
+      </c>
+      <c r="H19" s="12">
+        <v>195</v>
+      </c>
+      <c r="I19" s="4">
+        <f t="shared" si="2"/>
+        <v>1079</v>
+      </c>
+      <c r="J19" s="4">
+        <f t="shared" si="3"/>
+        <v>361</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N19" s="5" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" s="13">

--- a/data/12616002.xlsx
+++ b/data/12616002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA391D56-681A-4E05-90DE-44C9F8083A89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25F9A642-6479-4A08-ADA3-051F7CB1645F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="41">
   <si>
     <t>My Data, My Story</t>
   </si>
@@ -1383,25 +1383,47 @@
       <c r="A20" s="13">
         <v>46269</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J20" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
-      <c r="N20" s="5"/>
+      <c r="B20" s="3">
+        <v>462</v>
+      </c>
+      <c r="C20" s="12">
+        <v>30</v>
+      </c>
+      <c r="D20" s="12">
+        <v>143</v>
+      </c>
+      <c r="E20" s="12">
+        <v>120</v>
+      </c>
+      <c r="F20" s="12">
+        <v>250</v>
+      </c>
+      <c r="G20" s="12">
+        <v>5</v>
+      </c>
+      <c r="H20" s="12">
+        <v>234</v>
+      </c>
+      <c r="I20" s="4">
+        <f t="shared" si="2"/>
+        <v>1239</v>
+      </c>
+      <c r="J20" s="4">
+        <f t="shared" si="3"/>
+        <v>201</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N20" s="5" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="13">

--- a/data/12616002.xlsx
+++ b/data/12616002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25F9A642-6479-4A08-ADA3-051F7CB1645F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C6C438C-F5D5-45D7-A4F7-FED1CB734EF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="41">
   <si>
     <t>My Data, My Story</t>
   </si>
@@ -1429,25 +1429,47 @@
       <c r="A21" s="13">
         <v>46270</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J21" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
-      <c r="N21" s="5"/>
+      <c r="B21" s="3">
+        <v>485</v>
+      </c>
+      <c r="C21" s="12">
+        <v>0</v>
+      </c>
+      <c r="D21" s="12">
+        <v>108</v>
+      </c>
+      <c r="E21" s="12">
+        <v>197</v>
+      </c>
+      <c r="F21" s="12">
+        <v>0</v>
+      </c>
+      <c r="G21" s="12">
+        <v>0</v>
+      </c>
+      <c r="H21" s="12">
+        <v>129</v>
+      </c>
+      <c r="I21" s="4">
+        <f t="shared" si="2"/>
+        <v>919</v>
+      </c>
+      <c r="J21" s="4">
+        <f t="shared" si="3"/>
+        <v>521</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N21" s="5" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" s="13">

--- a/data/12616002.xlsx
+++ b/data/12616002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C6C438C-F5D5-45D7-A4F7-FED1CB734EF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F305A881-73BA-471A-8939-493DA0901894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="41">
   <si>
     <t>My Data, My Story</t>
   </si>
@@ -1475,25 +1475,47 @@
       <c r="A22" s="13">
         <v>46271</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J22" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
-      <c r="M22" s="3"/>
-      <c r="N22" s="5"/>
+      <c r="B22" s="3">
+        <v>473</v>
+      </c>
+      <c r="C22" s="12">
+        <v>40</v>
+      </c>
+      <c r="D22" s="12">
+        <v>107</v>
+      </c>
+      <c r="E22" s="12">
+        <v>121</v>
+      </c>
+      <c r="F22" s="12">
+        <v>0</v>
+      </c>
+      <c r="G22" s="12">
+        <v>0</v>
+      </c>
+      <c r="H22" s="12">
+        <v>243</v>
+      </c>
+      <c r="I22" s="4">
+        <f t="shared" si="2"/>
+        <v>984</v>
+      </c>
+      <c r="J22" s="4">
+        <f t="shared" si="3"/>
+        <v>456</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N22" s="5" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" s="13">

--- a/data/12616002.xlsx
+++ b/data/12616002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F305A881-73BA-471A-8939-493DA0901894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2123DF21-DB61-4FE4-BBFF-A8EEC772931D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="41">
   <si>
     <t>My Data, My Story</t>
   </si>
@@ -1521,25 +1521,47 @@
       <c r="A23" s="13">
         <v>46272</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J23" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
-      <c r="M23" s="3"/>
-      <c r="N23" s="5"/>
+      <c r="B23" s="3">
+        <v>440</v>
+      </c>
+      <c r="C23" s="12">
+        <v>30</v>
+      </c>
+      <c r="D23" s="12">
+        <v>130</v>
+      </c>
+      <c r="E23" s="12">
+        <v>158</v>
+      </c>
+      <c r="F23" s="12">
+        <v>100</v>
+      </c>
+      <c r="G23" s="12">
+        <v>2</v>
+      </c>
+      <c r="H23" s="12">
+        <v>279</v>
+      </c>
+      <c r="I23" s="4">
+        <f t="shared" si="2"/>
+        <v>1137</v>
+      </c>
+      <c r="J23" s="4">
+        <f t="shared" si="3"/>
+        <v>303</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N23" s="5" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" s="13">

--- a/data/12616002.xlsx
+++ b/data/12616002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2123DF21-DB61-4FE4-BBFF-A8EEC772931D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FA8849A-DA37-44EB-B096-597A2FD50184}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="41">
   <si>
     <t>My Data, My Story</t>
   </si>
@@ -1567,25 +1567,47 @@
       <c r="A24" s="13">
         <v>46273</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J24" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="M24" s="3"/>
-      <c r="N24" s="5"/>
+      <c r="B24" s="3">
+        <v>429</v>
+      </c>
+      <c r="C24" s="12">
+        <v>30</v>
+      </c>
+      <c r="D24" s="12">
+        <v>125</v>
+      </c>
+      <c r="E24" s="12">
+        <v>194</v>
+      </c>
+      <c r="F24" s="12">
+        <v>200</v>
+      </c>
+      <c r="G24" s="12">
+        <v>4</v>
+      </c>
+      <c r="H24" s="12">
+        <v>246</v>
+      </c>
+      <c r="I24" s="4">
+        <f t="shared" si="2"/>
+        <v>1224</v>
+      </c>
+      <c r="J24" s="4">
+        <f t="shared" si="3"/>
+        <v>216</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N24" s="5" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" s="13">

--- a/data/12616002.xlsx
+++ b/data/12616002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FA8849A-DA37-44EB-B096-597A2FD50184}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E26CAE58-BD87-4BFC-8A8C-E6E9664A7982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="41">
   <si>
     <t>My Data, My Story</t>
   </si>
@@ -1613,25 +1613,47 @@
       <c r="A25" s="13">
         <v>46274</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J25" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="5"/>
+      <c r="B25" s="3">
+        <v>422</v>
+      </c>
+      <c r="C25" s="12">
+        <v>40</v>
+      </c>
+      <c r="D25" s="12">
+        <v>90</v>
+      </c>
+      <c r="E25" s="12">
+        <v>164</v>
+      </c>
+      <c r="F25" s="12">
+        <v>200</v>
+      </c>
+      <c r="G25" s="12">
+        <v>4</v>
+      </c>
+      <c r="H25" s="12">
+        <v>172</v>
+      </c>
+      <c r="I25" s="4">
+        <f t="shared" si="2"/>
+        <v>1088</v>
+      </c>
+      <c r="J25" s="4">
+        <f t="shared" si="3"/>
+        <v>352</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N25" s="5" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" s="13">

--- a/data/12616002.xlsx
+++ b/data/12616002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E26CAE58-BD87-4BFC-8A8C-E6E9664A7982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{794A69A2-D342-4A37-B9FB-3354B7071CA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="41">
   <si>
     <t>My Data, My Story</t>
   </si>
@@ -1659,25 +1659,47 @@
       <c r="A26" s="13">
         <v>46275</v>
       </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="12"/>
-      <c r="I26" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J26" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
-      <c r="M26" s="3"/>
-      <c r="N26" s="5"/>
+      <c r="B26" s="3">
+        <v>479</v>
+      </c>
+      <c r="C26" s="12">
+        <v>40</v>
+      </c>
+      <c r="D26" s="12">
+        <v>186</v>
+      </c>
+      <c r="E26" s="12">
+        <v>139</v>
+      </c>
+      <c r="F26" s="12">
+        <v>100</v>
+      </c>
+      <c r="G26" s="12">
+        <v>2</v>
+      </c>
+      <c r="H26" s="12">
+        <v>247</v>
+      </c>
+      <c r="I26" s="4">
+        <f t="shared" si="2"/>
+        <v>1191</v>
+      </c>
+      <c r="J26" s="4">
+        <f t="shared" si="3"/>
+        <v>249</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N26" s="5" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" s="13">

--- a/data/12616002.xlsx
+++ b/data/12616002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{794A69A2-D342-4A37-B9FB-3354B7071CA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48076770-8742-43A5-9982-BDFD67AE4081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="41">
   <si>
     <t>My Data, My Story</t>
   </si>
@@ -1705,25 +1705,47 @@
       <c r="A27" s="13">
         <v>46276</v>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J27" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-      <c r="M27" s="3"/>
-      <c r="N27" s="5"/>
+      <c r="B27" s="3">
+        <v>455</v>
+      </c>
+      <c r="C27" s="12">
+        <v>40</v>
+      </c>
+      <c r="D27" s="12">
+        <v>90</v>
+      </c>
+      <c r="E27" s="12">
+        <v>162</v>
+      </c>
+      <c r="F27" s="12">
+        <v>250</v>
+      </c>
+      <c r="G27" s="12">
+        <v>5</v>
+      </c>
+      <c r="H27" s="12">
+        <v>151</v>
+      </c>
+      <c r="I27" s="4">
+        <f t="shared" si="2"/>
+        <v>1148</v>
+      </c>
+      <c r="J27" s="4">
+        <f t="shared" si="3"/>
+        <v>292</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N27" s="5" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" s="13">

--- a/data/12616002.xlsx
+++ b/data/12616002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48076770-8742-43A5-9982-BDFD67AE4081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D27E1C30-E234-4C79-9423-8D44912DF4D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="41">
   <si>
     <t>My Data, My Story</t>
   </si>
@@ -1751,25 +1751,47 @@
       <c r="A28" s="13">
         <v>46277</v>
       </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J28" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3"/>
-      <c r="N28" s="5"/>
+      <c r="B28" s="3">
+        <v>536</v>
+      </c>
+      <c r="C28" s="12">
+        <v>30</v>
+      </c>
+      <c r="D28" s="12">
+        <v>74</v>
+      </c>
+      <c r="E28" s="12">
+        <v>60</v>
+      </c>
+      <c r="F28" s="12">
+        <v>0</v>
+      </c>
+      <c r="G28" s="12">
+        <v>0</v>
+      </c>
+      <c r="H28" s="12">
+        <v>147</v>
+      </c>
+      <c r="I28" s="4">
+        <f t="shared" si="2"/>
+        <v>847</v>
+      </c>
+      <c r="J28" s="4">
+        <f t="shared" si="3"/>
+        <v>593</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N28" s="5" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="13">

--- a/data/12616002.xlsx
+++ b/data/12616002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D27E1C30-E234-4C79-9423-8D44912DF4D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C7E2442-709D-4825-B9E9-51357722E68D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="41">
   <si>
     <t>My Data, My Story</t>
   </si>
@@ -1797,25 +1797,47 @@
       <c r="A29" s="13">
         <v>46278</v>
       </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J29" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K29" s="3"/>
-      <c r="L29" s="3"/>
-      <c r="M29" s="3"/>
-      <c r="N29" s="5"/>
+      <c r="B29" s="3">
+        <v>469</v>
+      </c>
+      <c r="C29" s="12">
+        <v>30</v>
+      </c>
+      <c r="D29" s="12">
+        <v>154</v>
+      </c>
+      <c r="E29" s="12">
+        <v>146</v>
+      </c>
+      <c r="F29" s="12">
+        <v>0</v>
+      </c>
+      <c r="G29" s="12">
+        <v>0</v>
+      </c>
+      <c r="H29" s="12">
+        <v>308</v>
+      </c>
+      <c r="I29" s="4">
+        <f t="shared" si="2"/>
+        <v>1107</v>
+      </c>
+      <c r="J29" s="4">
+        <f t="shared" si="3"/>
+        <v>333</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N29" s="5" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" s="13">

--- a/data/12616002.xlsx
+++ b/data/12616002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C7E2442-709D-4825-B9E9-51357722E68D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7EE854D-183F-4178-BC40-7E8BA102F64F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="41">
   <si>
     <t>My Data, My Story</t>
   </si>
@@ -1843,25 +1843,47 @@
       <c r="A30" s="13">
         <v>46279</v>
       </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J30" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K30" s="3"/>
-      <c r="L30" s="3"/>
-      <c r="M30" s="3"/>
-      <c r="N30" s="5"/>
+      <c r="B30" s="3">
+        <v>420</v>
+      </c>
+      <c r="C30" s="12">
+        <v>60</v>
+      </c>
+      <c r="D30" s="12">
+        <v>131</v>
+      </c>
+      <c r="E30" s="12">
+        <v>247</v>
+      </c>
+      <c r="F30" s="12">
+        <v>200</v>
+      </c>
+      <c r="G30" s="12">
+        <v>4</v>
+      </c>
+      <c r="H30" s="12">
+        <v>159</v>
+      </c>
+      <c r="I30" s="4">
+        <f t="shared" si="2"/>
+        <v>1217</v>
+      </c>
+      <c r="J30" s="4">
+        <f t="shared" si="3"/>
+        <v>223</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M30" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N30" s="5" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" s="13">

--- a/data/12616002.xlsx
+++ b/data/12616002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7EE854D-183F-4178-BC40-7E8BA102F64F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE0A7904-EEA3-4EFE-B14B-51D64E0CBDBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="41">
   <si>
     <t>My Data, My Story</t>
   </si>
@@ -1889,25 +1889,47 @@
       <c r="A31" s="13">
         <v>46280</v>
       </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J31" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K31" s="3"/>
-      <c r="L31" s="3"/>
-      <c r="M31" s="3"/>
-      <c r="N31" s="5"/>
+      <c r="B31" s="3">
+        <v>420</v>
+      </c>
+      <c r="C31" s="12">
+        <v>60</v>
+      </c>
+      <c r="D31" s="12">
+        <v>131</v>
+      </c>
+      <c r="E31" s="12">
+        <v>247</v>
+      </c>
+      <c r="F31" s="12">
+        <v>200</v>
+      </c>
+      <c r="G31" s="12">
+        <v>4</v>
+      </c>
+      <c r="H31" s="12">
+        <v>159</v>
+      </c>
+      <c r="I31" s="4">
+        <f t="shared" si="2"/>
+        <v>1217</v>
+      </c>
+      <c r="J31" s="4">
+        <f t="shared" si="3"/>
+        <v>223</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M31" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N31" s="5" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" s="13">

--- a/data/12616002.xlsx
+++ b/data/12616002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE0A7904-EEA3-4EFE-B14B-51D64E0CBDBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AC3A7B3-41A9-49AF-911A-B5748D264F96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="41">
   <si>
     <t>My Data, My Story</t>
   </si>
@@ -1935,25 +1935,47 @@
       <c r="A32" s="13">
         <v>46281</v>
       </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="12"/>
-      <c r="H32" s="12"/>
-      <c r="I32" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J32" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K32" s="3"/>
-      <c r="L32" s="3"/>
-      <c r="M32" s="3"/>
-      <c r="N32" s="5"/>
+      <c r="B32" s="3">
+        <v>467</v>
+      </c>
+      <c r="C32" s="12">
+        <v>30</v>
+      </c>
+      <c r="D32" s="12">
+        <v>101</v>
+      </c>
+      <c r="E32" s="12">
+        <v>194</v>
+      </c>
+      <c r="F32" s="12">
+        <v>150</v>
+      </c>
+      <c r="G32" s="12">
+        <v>3</v>
+      </c>
+      <c r="H32" s="12">
+        <v>187</v>
+      </c>
+      <c r="I32" s="4">
+        <f t="shared" si="2"/>
+        <v>1129</v>
+      </c>
+      <c r="J32" s="4">
+        <f t="shared" si="3"/>
+        <v>311</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N32" s="5" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" s="13">

--- a/data/12616002.xlsx
+++ b/data/12616002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AC3A7B3-41A9-49AF-911A-B5748D264F96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44195D5D-CD9F-4FAA-9B28-23483233FBCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="41">
   <si>
     <t>My Data, My Story</t>
   </si>
@@ -1981,25 +1981,47 @@
       <c r="A33" s="13">
         <v>46282</v>
       </c>
-      <c r="B33" s="3"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J33" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K33" s="3"/>
-      <c r="L33" s="3"/>
-      <c r="M33" s="3"/>
-      <c r="N33" s="5"/>
+      <c r="B33" s="3">
+        <v>414</v>
+      </c>
+      <c r="C33" s="12">
+        <v>0</v>
+      </c>
+      <c r="D33" s="12">
+        <v>78</v>
+      </c>
+      <c r="E33" s="12">
+        <v>167</v>
+      </c>
+      <c r="F33" s="12">
+        <v>250</v>
+      </c>
+      <c r="G33" s="12">
+        <v>5</v>
+      </c>
+      <c r="H33" s="12">
+        <v>204</v>
+      </c>
+      <c r="I33" s="4">
+        <f t="shared" si="2"/>
+        <v>1113</v>
+      </c>
+      <c r="J33" s="4">
+        <f>IF(I33="","",1440-I33)</f>
+        <v>327</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N33" s="5" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" s="13">

--- a/data/12616002.xlsx
+++ b/data/12616002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44195D5D-CD9F-4FAA-9B28-23483233FBCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DC7B149-CABB-4C10-991A-DA7474F54845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="41">
   <si>
     <t>My Data, My Story</t>
   </si>
@@ -2027,25 +2027,47 @@
       <c r="A34" s="13">
         <v>46283</v>
       </c>
-      <c r="B34" s="3"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="12"/>
-      <c r="I34" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J34" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K34" s="3"/>
-      <c r="L34" s="3"/>
-      <c r="M34" s="3"/>
-      <c r="N34" s="5"/>
+      <c r="B34" s="3">
+        <v>460</v>
+      </c>
+      <c r="C34" s="12">
+        <v>0</v>
+      </c>
+      <c r="D34" s="12">
+        <v>113</v>
+      </c>
+      <c r="E34" s="12">
+        <v>168</v>
+      </c>
+      <c r="F34" s="12">
+        <v>250</v>
+      </c>
+      <c r="G34" s="12">
+        <v>5</v>
+      </c>
+      <c r="H34" s="12">
+        <v>266</v>
+      </c>
+      <c r="I34" s="4">
+        <f t="shared" si="2"/>
+        <v>1257</v>
+      </c>
+      <c r="J34" s="4">
+        <f t="shared" si="3"/>
+        <v>183</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M34" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N34" s="5" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" s="13">

--- a/data/12616002.xlsx
+++ b/data/12616002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DC7B149-CABB-4C10-991A-DA7474F54845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35FCFCE7-9DDE-4291-82D3-66DF70531B93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="41">
   <si>
     <t>My Data, My Story</t>
   </si>
@@ -2073,25 +2073,47 @@
       <c r="A35" s="13">
         <v>46284</v>
       </c>
-      <c r="B35" s="3"/>
-      <c r="C35" s="12"/>
-      <c r="D35" s="12"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="12"/>
-      <c r="H35" s="12"/>
-      <c r="I35" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J35" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K35" s="3"/>
-      <c r="L35" s="3"/>
-      <c r="M35" s="3"/>
-      <c r="N35" s="5"/>
+      <c r="B35" s="3">
+        <v>501</v>
+      </c>
+      <c r="C35" s="12">
+        <v>60</v>
+      </c>
+      <c r="D35" s="12">
+        <v>118</v>
+      </c>
+      <c r="E35" s="12">
+        <v>121</v>
+      </c>
+      <c r="F35" s="12">
+        <v>0</v>
+      </c>
+      <c r="G35" s="12">
+        <v>0</v>
+      </c>
+      <c r="H35" s="12">
+        <v>239</v>
+      </c>
+      <c r="I35" s="4">
+        <f t="shared" si="2"/>
+        <v>1039</v>
+      </c>
+      <c r="J35" s="4">
+        <f t="shared" si="3"/>
+        <v>401</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N35" s="5" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" s="13">

--- a/data/12616002.xlsx
+++ b/data/12616002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35FCFCE7-9DDE-4291-82D3-66DF70531B93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B03BF50D-307F-422C-9549-983ED49920FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="41">
   <si>
     <t>My Data, My Story</t>
   </si>
@@ -2119,25 +2119,47 @@
       <c r="A36" s="13">
         <v>46285</v>
       </c>
-      <c r="B36" s="3"/>
-      <c r="C36" s="12"/>
-      <c r="D36" s="12"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="12"/>
-      <c r="H36" s="12"/>
-      <c r="I36" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J36" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K36" s="3"/>
-      <c r="L36" s="3"/>
-      <c r="M36" s="3"/>
-      <c r="N36" s="5"/>
+      <c r="B36" s="3">
+        <v>453</v>
+      </c>
+      <c r="C36" s="12">
+        <v>30</v>
+      </c>
+      <c r="D36" s="12">
+        <v>120</v>
+      </c>
+      <c r="E36" s="12">
+        <v>208</v>
+      </c>
+      <c r="F36" s="12">
+        <v>0</v>
+      </c>
+      <c r="G36" s="12">
+        <v>0</v>
+      </c>
+      <c r="H36" s="12">
+        <v>267</v>
+      </c>
+      <c r="I36" s="4">
+        <f t="shared" si="2"/>
+        <v>1078</v>
+      </c>
+      <c r="J36" s="4">
+        <f t="shared" si="3"/>
+        <v>362</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="M36" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N36" s="5" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" s="13">

--- a/data/12616002.xlsx
+++ b/data/12616002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B03BF50D-307F-422C-9549-983ED49920FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D5C4F48-3AE5-4B51-A2AE-509C38D3EA47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="41">
   <si>
     <t>My Data, My Story</t>
   </si>
@@ -2165,25 +2165,47 @@
       <c r="A37" s="13">
         <v>46286</v>
       </c>
-      <c r="B37" s="3"/>
-      <c r="C37" s="12"/>
-      <c r="D37" s="12"/>
-      <c r="E37" s="12"/>
-      <c r="F37" s="12"/>
-      <c r="G37" s="12"/>
-      <c r="H37" s="12"/>
-      <c r="I37" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J37" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K37" s="3"/>
-      <c r="L37" s="3"/>
-      <c r="M37" s="3"/>
-      <c r="N37" s="5"/>
+      <c r="B37" s="3">
+        <v>458</v>
+      </c>
+      <c r="C37" s="12">
+        <v>40</v>
+      </c>
+      <c r="D37" s="12">
+        <v>122</v>
+      </c>
+      <c r="E37" s="12">
+        <v>205</v>
+      </c>
+      <c r="F37" s="12">
+        <v>200</v>
+      </c>
+      <c r="G37" s="12">
+        <v>4</v>
+      </c>
+      <c r="H37" s="12">
+        <v>238</v>
+      </c>
+      <c r="I37" s="4">
+        <f t="shared" si="2"/>
+        <v>1263</v>
+      </c>
+      <c r="J37" s="4">
+        <f t="shared" si="3"/>
+        <v>177</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M37" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N37" s="5" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" s="13">

--- a/data/12616002.xlsx
+++ b/data/12616002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D5C4F48-3AE5-4B51-A2AE-509C38D3EA47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1DA3CC9-BAE2-4C96-AC89-795F88535628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="41">
   <si>
     <t>My Data, My Story</t>
   </si>
@@ -2211,25 +2211,47 @@
       <c r="A38" s="13">
         <v>46287</v>
       </c>
-      <c r="B38" s="3"/>
-      <c r="C38" s="12"/>
-      <c r="D38" s="12"/>
-      <c r="E38" s="12"/>
-      <c r="F38" s="12"/>
-      <c r="G38" s="12"/>
-      <c r="H38" s="12"/>
-      <c r="I38" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J38" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K38" s="3"/>
-      <c r="L38" s="3"/>
-      <c r="M38" s="3"/>
-      <c r="N38" s="5"/>
+      <c r="B38" s="3">
+        <v>485</v>
+      </c>
+      <c r="C38" s="12">
+        <v>60</v>
+      </c>
+      <c r="D38" s="12">
+        <v>157</v>
+      </c>
+      <c r="E38" s="12">
+        <v>133</v>
+      </c>
+      <c r="F38" s="12">
+        <v>150</v>
+      </c>
+      <c r="G38" s="12">
+        <v>3</v>
+      </c>
+      <c r="H38" s="12">
+        <v>214</v>
+      </c>
+      <c r="I38" s="4">
+        <f t="shared" si="2"/>
+        <v>1199</v>
+      </c>
+      <c r="J38" s="4">
+        <f t="shared" si="3"/>
+        <v>241</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M38" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N38" s="5" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39" s="13">

--- a/data/12616002.xlsx
+++ b/data/12616002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1DA3CC9-BAE2-4C96-AC89-795F88535628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47930BA2-DE8F-421D-BD29-3E2036C06C1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="41">
   <si>
     <t>My Data, My Story</t>
   </si>
@@ -2257,25 +2257,47 @@
       <c r="A39" s="13">
         <v>46288</v>
       </c>
-      <c r="B39" s="3"/>
-      <c r="C39" s="12"/>
-      <c r="D39" s="12"/>
-      <c r="E39" s="12"/>
-      <c r="F39" s="12"/>
-      <c r="G39" s="12"/>
-      <c r="H39" s="12"/>
-      <c r="I39" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J39" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K39" s="3"/>
-      <c r="L39" s="3"/>
-      <c r="M39" s="3"/>
-      <c r="N39" s="5"/>
+      <c r="B39" s="3">
+        <v>450</v>
+      </c>
+      <c r="C39" s="12">
+        <v>60</v>
+      </c>
+      <c r="D39" s="12">
+        <v>120</v>
+      </c>
+      <c r="E39" s="12">
+        <v>134</v>
+      </c>
+      <c r="F39" s="12">
+        <v>156</v>
+      </c>
+      <c r="G39" s="12">
+        <v>6</v>
+      </c>
+      <c r="H39" s="12">
+        <v>245</v>
+      </c>
+      <c r="I39" s="4">
+        <f>IF(COUNT(B39:F39,H39)&lt;6,"",SUM(B39:F39,H39))</f>
+        <v>1165</v>
+      </c>
+      <c r="J39" s="4">
+        <f t="shared" si="3"/>
+        <v>275</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M39" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N39" s="5" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A40" s="13">

--- a/data/12616002.xlsx
+++ b/data/12616002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47930BA2-DE8F-421D-BD29-3E2036C06C1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99CA2DFA-5270-4CD1-864C-E6ADC45B7D94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="41">
   <si>
     <t>My Data, My Story</t>
   </si>
@@ -2303,25 +2303,47 @@
       <c r="A40" s="13">
         <v>46289</v>
       </c>
-      <c r="B40" s="3"/>
-      <c r="C40" s="12"/>
-      <c r="D40" s="12"/>
-      <c r="E40" s="12"/>
-      <c r="F40" s="12"/>
-      <c r="G40" s="12"/>
-      <c r="H40" s="12"/>
-      <c r="I40" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J40" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K40" s="3"/>
-      <c r="L40" s="3"/>
-      <c r="M40" s="3"/>
-      <c r="N40" s="5"/>
+      <c r="B40" s="3">
+        <v>485</v>
+      </c>
+      <c r="C40" s="12">
+        <v>30</v>
+      </c>
+      <c r="D40" s="12">
+        <v>144</v>
+      </c>
+      <c r="E40" s="12">
+        <v>64</v>
+      </c>
+      <c r="F40" s="12">
+        <v>200</v>
+      </c>
+      <c r="G40" s="12">
+        <v>4</v>
+      </c>
+      <c r="H40" s="12">
+        <v>221</v>
+      </c>
+      <c r="I40" s="4">
+        <f t="shared" si="2"/>
+        <v>1144</v>
+      </c>
+      <c r="J40" s="4">
+        <f t="shared" si="3"/>
+        <v>296</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M40" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N40" s="5" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A41" s="13">

--- a/data/12616002.xlsx
+++ b/data/12616002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99CA2DFA-5270-4CD1-864C-E6ADC45B7D94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64D7C169-D449-4495-82A3-5318E2F79637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="41">
   <si>
     <t>My Data, My Story</t>
   </si>
@@ -2349,25 +2349,47 @@
       <c r="A41" s="13">
         <v>46290</v>
       </c>
-      <c r="B41" s="3"/>
-      <c r="C41" s="12"/>
-      <c r="D41" s="12"/>
-      <c r="E41" s="12"/>
-      <c r="F41" s="12"/>
-      <c r="G41" s="12"/>
-      <c r="H41" s="12"/>
-      <c r="I41" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J41" s="4" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K41" s="3"/>
-      <c r="L41" s="3"/>
-      <c r="M41" s="3"/>
-      <c r="N41" s="5"/>
+      <c r="B41" s="3">
+        <v>486</v>
+      </c>
+      <c r="C41" s="12">
+        <v>0</v>
+      </c>
+      <c r="D41" s="12">
+        <v>143</v>
+      </c>
+      <c r="E41" s="12">
+        <v>60</v>
+      </c>
+      <c r="F41" s="12">
+        <v>250</v>
+      </c>
+      <c r="G41" s="12">
+        <v>5</v>
+      </c>
+      <c r="H41" s="12">
+        <v>213</v>
+      </c>
+      <c r="I41" s="4">
+        <f t="shared" si="2"/>
+        <v>1152</v>
+      </c>
+      <c r="J41" s="4">
+        <f t="shared" si="3"/>
+        <v>288</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M41" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N41" s="5" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A42" s="13">
